--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,22 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B539881-35F2-4ACF-93AE-EB11A251A4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="21075" windowHeight="10050"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId2"/>
     <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -104,7 +116,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -172,9 +184,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -212,9 +224,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -249,7 +261,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -284,7 +296,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -457,16 +469,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -474,47 +486,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -525,18 +537,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1328125" customWidth="1"/>
-    <col min="2" max="8" width="14.3984375" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -562,59 +574,66 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>7.5999999999999998E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <v>7.5999999999999998E-2</v>
+        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
-        <v>7.8E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E2">
-        <v>7.5999999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F2">
-        <v>7.5999999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G2">
-        <v>7.5999999999999998E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H2">
-        <v>7.5999999999999998E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="C3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="D3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="E3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="F3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="G3">
-        <v>4.2700000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="H3">
-        <v>4.2700000000000002E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -640,7 +659,7 @@
         <v>4.1599999999999998E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -666,7 +685,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -692,30 +711,30 @@
         <v>2.9819999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="C7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="D7">
-        <v>5.8000000000000003E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="E7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="F7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="G7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
       <c r="H7">
-        <v>5.8700000000000002E-2</v>
+        <v>5.8500000000000003E-2</v>
       </c>
     </row>
   </sheetData>
@@ -724,18 +743,18 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:H7"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1328125" customWidth="1"/>
-    <col min="2" max="8" width="14.3984375" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="8" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="4" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -761,85 +780,99 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>7.1999999999999995E-2</v>
+        <f>1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="C2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" ref="C2:H2" si="0">1/17</f>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="D2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="E2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="F2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="G2">
-        <v>7.1999999999999995E-2</v>
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
       </c>
       <c r="H2">
-        <v>7.1999999999999995E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+        <f t="shared" si="0"/>
+        <v>5.8823529411764705E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>3.5499999999999997E-2</v>
+        <f>1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="C3">
-        <v>3.5499999999999997E-2</v>
+        <f t="shared" ref="C3:H3" si="1">1/19</f>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="D3">
-        <v>3.5499999999999997E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="E3">
-        <v>3.5499999999999997E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="F3">
-        <v>3.5499999999999997E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="G3">
-        <v>3.5499999999999997E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
       </c>
       <c r="H3">
-        <v>3.5499999999999997E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+        <f t="shared" si="1"/>
+        <v>5.2631578947368418E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="C4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="D4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="E4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="F4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="G4">
-        <v>4.2000000000000003E-2</v>
+        <v>2.8000000000000001E-2</v>
       </c>
       <c r="H4">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+        <v>2.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>15</v>
       </c>
@@ -865,7 +898,7 @@
         <v>2.9000000000000001E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>16</v>
       </c>
@@ -891,7 +924,7 @@
         <v>3.0300000000000001E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
